--- a/results/model_results.xlsx
+++ b/results/model_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Imagery</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>OA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OA Std (KFold)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Kappa</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Kappa Std (KFold)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Training Time (s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Training Time Std (s)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Validation Time (s)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Validation Time Std (s)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Classification Time (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Classification Time Std (s)</t>
         </is>
@@ -514,16 +502,16 @@
         <v>0.003278</v>
       </c>
       <c r="G2" t="n">
-        <v>0.773436</v>
+        <v>0.370175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000395</v>
+        <v>0.006426</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001208</v>
+        <v>0.000796</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000126</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -552,16 +540,16 @@
         <v>0.002741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.060301</v>
+        <v>0.0492</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001136</v>
+        <v>0.003987</v>
       </c>
       <c r="I3" t="n">
-        <v>0.803032</v>
+        <v>0.187864</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001076</v>
+        <v>0.001939</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -574,32 +562,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SGDC</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.975167</v>
+        <v>0.979917</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002367</v>
+        <v>0.001547</v>
       </c>
       <c r="E4" t="n">
-        <v>0.96275</v>
+        <v>0.969875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00355</v>
+        <v>0.00232</v>
       </c>
       <c r="G4" t="n">
-        <v>0.080887</v>
+        <v>9.673875000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001042</v>
+        <v>0.033842</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009940000000000001</v>
+        <v>0.005493</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000525</v>
+        <v>0.001445</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -612,32 +600,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LinearSVC</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.97375</v>
+        <v>0.980083</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002024</v>
+        <v>0.001112</v>
       </c>
       <c r="E5" t="n">
-        <v>0.960625</v>
+        <v>0.970125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003035</v>
+        <v>0.001667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.13965</v>
+        <v>5.728813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002652</v>
+        <v>0.009675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000724</v>
+        <v>0.051238</v>
       </c>
       <c r="J5" t="n">
-        <v>9.8e-05</v>
+        <v>0.000508</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -645,37 +633,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S2_2</t>
+          <t>S2_1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>SGDC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.974583</v>
+        <v>0.976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001674</v>
+        <v>0.002295</v>
       </c>
       <c r="E6" t="n">
-        <v>0.961875</v>
+        <v>0.964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002512</v>
+        <v>0.003442</v>
       </c>
       <c r="G6" t="n">
-        <v>2.108655</v>
+        <v>0.05419</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002257</v>
+        <v>0.006565</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00148</v>
+        <v>0.000448</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000216</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -683,37 +671,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S2_2</t>
+          <t>S2_1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LinearSVC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.98075</v>
+        <v>0.97375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001009</v>
+        <v>0.002024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971125</v>
+        <v>0.960625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001514</v>
+        <v>0.003035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006602</v>
+        <v>0.074847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002607</v>
+        <v>0.001934</v>
       </c>
       <c r="I7" t="n">
-        <v>0.736737</v>
+        <v>0.000486</v>
       </c>
       <c r="J7" t="n">
-        <v>0.011006</v>
+        <v>0.000105</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -721,37 +709,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S2_2</t>
+          <t>S2_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SGDC</t>
+          <t>SVM_rbf</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.984833</v>
+        <v>0.982</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001794</v>
+        <v>0.002321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.97725</v>
+        <v>0.973</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00269</v>
+        <v>0.003481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.138512</v>
+        <v>1.245056</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00168</v>
+        <v>0.003103</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001516</v>
+        <v>1.178993</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000801</v>
+        <v>0.002685</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -764,32 +752,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LinearSVC</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.978417</v>
+        <v>0.974583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001855</v>
+        <v>0.001674</v>
       </c>
       <c r="E9" t="n">
-        <v>0.967625</v>
+        <v>0.961875</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002782</v>
+        <v>0.002512</v>
       </c>
       <c r="G9" t="n">
-        <v>0.340696</v>
+        <v>1.018387</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003144</v>
+        <v>0.004821</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001012</v>
+        <v>0.001212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000126</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -797,37 +785,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PS_1</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.932083</v>
+        <v>0.98075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002071</v>
+        <v>0.001009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.898125</v>
+        <v>0.971125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003106</v>
+        <v>0.001514</v>
       </c>
       <c r="G10" t="n">
-        <v>0.469754</v>
+        <v>0.007206</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001308</v>
+        <v>0.002709</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001142</v>
+        <v>0.882917</v>
       </c>
       <c r="J10" t="n">
-        <v>6.7e-05</v>
+        <v>0.9043</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -835,37 +823,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PS_1</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.955667</v>
+        <v>0.985917</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001506</v>
+        <v>0.001083</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9335</v>
+        <v>0.9788750000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00226</v>
+        <v>0.001624</v>
       </c>
       <c r="G11" t="n">
-        <v>0.060356</v>
+        <v>10.811818</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001378</v>
+        <v>0.034841</v>
       </c>
       <c r="I11" t="n">
-        <v>0.867468</v>
+        <v>0.004996</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001327</v>
+        <v>0.00022</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -873,37 +861,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PS_1</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SGDC</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.925417</v>
+        <v>0.98425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00277</v>
+        <v>0.001369</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8881250000000001</v>
+        <v>0.976375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004154</v>
+        <v>0.002053</v>
       </c>
       <c r="G12" t="n">
-        <v>0.082177</v>
+        <v>9.926339</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000659</v>
+        <v>0.044033</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000676</v>
+        <v>0.05004</v>
       </c>
       <c r="J12" t="n">
-        <v>5.5e-05</v>
+        <v>5.8e-05</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -911,37 +899,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PS_1</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LinearSVC</t>
+          <t>SGDC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.922333</v>
+        <v>0.98475</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002709</v>
+        <v>0.001836</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8835</v>
+        <v>0.977125</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004063</v>
+        <v>0.002754</v>
       </c>
       <c r="G13" t="n">
-        <v>0.156483</v>
+        <v>0.095859</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001954</v>
+        <v>0.0033</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000738</v>
+        <v>0.001016</v>
       </c>
       <c r="J13" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -949,37 +937,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PS_2</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>LinearSVC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.945333</v>
+        <v>0.978333</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002457</v>
+        <v>0.001855</v>
       </c>
       <c r="E14" t="n">
-        <v>0.918</v>
+        <v>0.9675</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003686</v>
+        <v>0.002782</v>
       </c>
       <c r="G14" t="n">
-        <v>0.978312</v>
+        <v>0.196827</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000195</v>
+        <v>0.004036</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001312</v>
+        <v>0.000934</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000103</v>
+        <v>0.000139</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -987,37 +975,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PS_2</t>
+          <t>S2_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM_rbf</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.96025</v>
+        <v>0.99</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001167</v>
+        <v>0.002014</v>
       </c>
       <c r="E15" t="n">
-        <v>0.940375</v>
+        <v>0.985</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00175</v>
+        <v>0.00302</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004275</v>
+        <v>1.22013</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001248</v>
+        <v>0.004729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.749905</v>
+        <v>1.318475</v>
       </c>
       <c r="J15" t="n">
-        <v>0.049991</v>
+        <v>0.003242</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1025,37 +1013,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PS_2</t>
+          <t>PS_1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SGDC</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.956167</v>
+        <v>0.932083</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003344</v>
+        <v>0.002071</v>
       </c>
       <c r="E16" t="n">
-        <v>0.93425</v>
+        <v>0.898125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005015</v>
+        <v>0.003106</v>
       </c>
       <c r="G16" t="n">
-        <v>0.115152</v>
+        <v>0.271809</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000982</v>
+        <v>0.000869</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000941</v>
+        <v>0.000825</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000121</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1063,40 +1051,496 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PS_2</t>
+          <t>PS_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LinearSVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.955917</v>
+        <v>0.955667</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002456</v>
+        <v>0.001506</v>
       </c>
       <c r="E17" t="n">
-        <v>0.933875</v>
+        <v>0.9335</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003685</v>
+        <v>0.00226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330447</v>
+        <v>0.048434</v>
       </c>
       <c r="H17" t="n">
-        <v>0.008926999999999999</v>
+        <v>0.00433</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000975</v>
+        <v>0.218477</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000145</v>
+        <v>0.000922</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PS_1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.001864</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.002797</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.772275</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.035925</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.004728</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.000283</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PS_1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.963417</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.001397</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.945125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.002095</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.674549</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.023037</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.056326</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.000312</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PS_1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SGDC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.927917</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.002436</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.891875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.003654</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.065326</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.015522</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.000457</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.9e-05</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PS_1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LinearSVC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.922333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.002709</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8835</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.004063</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.08334</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.014733</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.000507</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.4e-05</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PS_1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SVM_rbf</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.970917</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.002104</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.956375</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.003156</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.302678</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.251402</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.003358</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.945333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.002457</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.003686</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.565312</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.004434</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.001191</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9.3e-05</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.96025</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.001167</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.940375</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.004109</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.245896</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.003989</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.001255</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.95425</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.001882</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.727097</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.252151</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.004829</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.000255</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.964333</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.001876</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.002814</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.156286</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.007215</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.055212</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.001072</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SGDC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.956667</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.002898</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.004347</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.083574</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.006024</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.001029</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.500000000000001e-05</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LinearSVC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.956083</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.002397</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.934125</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.003596</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.181578</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.013659</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.001067</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.000279</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PS_2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SVM_rbf</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.973583</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.001916</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.960375</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.002873</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.470116</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.586316</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.001784</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/model_results.xlsx
+++ b/results/model_results.xlsx
@@ -502,16 +502,16 @@
         <v>0.003278</v>
       </c>
       <c r="G2" t="n">
-        <v>0.370175</v>
+        <v>0.364895</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006426</v>
+        <v>0.004326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000796</v>
+        <v>0.000791</v>
       </c>
       <c r="J2" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>7.6e-05</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -540,16 +540,16 @@
         <v>0.002741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0492</v>
+        <v>0.048774</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003987</v>
+        <v>0.004747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187864</v>
+        <v>0.178129</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001939</v>
+        <v>0.00014</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -578,16 +578,16 @@
         <v>0.00232</v>
       </c>
       <c r="G4" t="n">
-        <v>9.673875000000001</v>
+        <v>9.730859000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.033842</v>
+        <v>0.0593</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005493</v>
+        <v>0.004879</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001445</v>
+        <v>0.000155</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -616,16 +616,16 @@
         <v>0.001667</v>
       </c>
       <c r="G5" t="n">
-        <v>5.728813</v>
+        <v>5.622407</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009675</v>
+        <v>0.039901</v>
       </c>
       <c r="I5" t="n">
-        <v>0.051238</v>
+        <v>0.051366</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000508</v>
+        <v>0.000351</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -654,16 +654,16 @@
         <v>0.003442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05419</v>
+        <v>0.053402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006565</v>
+        <v>0.005595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000448</v>
+        <v>0.000456</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9e-05</v>
+        <v>9.1e-05</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -692,16 +692,16 @@
         <v>0.003035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.074847</v>
+        <v>0.080661</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001934</v>
+        <v>0.006309</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000486</v>
+        <v>0.000489</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000105</v>
+        <v>8.2e-05</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVM_rbf</t>
+          <t>SVC_rbf</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -730,16 +730,16 @@
         <v>0.003481</v>
       </c>
       <c r="G8" t="n">
-        <v>1.245056</v>
+        <v>1.275501</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003103</v>
+        <v>0.029185</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178993</v>
+        <v>1.193824</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002685</v>
+        <v>0.001193</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -768,16 +768,16 @@
         <v>0.002512</v>
       </c>
       <c r="G9" t="n">
-        <v>1.018387</v>
+        <v>1.021407</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004821</v>
+        <v>0.006684</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001212</v>
+        <v>0.001169</v>
       </c>
       <c r="J9" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>6.3e-05</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -806,16 +806,16 @@
         <v>0.001514</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007206</v>
+        <v>0.004943</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002709</v>
+        <v>0.001205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.882917</v>
+        <v>1.160957</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9043</v>
+        <v>1.2791</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -844,16 +844,16 @@
         <v>0.001624</v>
       </c>
       <c r="G11" t="n">
-        <v>10.811818</v>
+        <v>10.80929</v>
       </c>
       <c r="H11" t="n">
-        <v>0.034841</v>
+        <v>0.09884900000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004996</v>
+        <v>0.004715</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00022</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -882,16 +882,16 @@
         <v>0.002053</v>
       </c>
       <c r="G12" t="n">
-        <v>9.926339</v>
+        <v>9.53619</v>
       </c>
       <c r="H12" t="n">
-        <v>0.044033</v>
+        <v>0.017483</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05004</v>
+        <v>0.049963</v>
       </c>
       <c r="J12" t="n">
-        <v>5.8e-05</v>
+        <v>0.000141</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -920,16 +920,16 @@
         <v>0.002754</v>
       </c>
       <c r="G13" t="n">
-        <v>0.095859</v>
+        <v>0.093955</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0033</v>
+        <v>0.001262</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001016</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9.899999999999999e-05</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -958,16 +958,16 @@
         <v>0.002782</v>
       </c>
       <c r="G14" t="n">
-        <v>0.196827</v>
+        <v>0.159695</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004036</v>
+        <v>0.005341</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000934</v>
+        <v>0.000926</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000139</v>
+        <v>0.000116</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SVM_rbf</t>
+          <t>SVC_rbf</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -996,16 +996,16 @@
         <v>0.00302</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22013</v>
+        <v>1.192658</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004729</v>
+        <v>0.033586</v>
       </c>
       <c r="I15" t="n">
-        <v>1.318475</v>
+        <v>1.146287</v>
       </c>
       <c r="J15" t="n">
-        <v>0.003242</v>
+        <v>0.004474</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1034,16 +1034,16 @@
         <v>0.003106</v>
       </c>
       <c r="G16" t="n">
-        <v>0.271809</v>
+        <v>0.274216</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000869</v>
+        <v>0.004364</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000825</v>
+        <v>0.000822</v>
       </c>
       <c r="J16" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
         <v>0.00226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.048434</v>
+        <v>0.04798</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00433</v>
+        <v>0.004462</v>
       </c>
       <c r="I17" t="n">
-        <v>0.218477</v>
+        <v>0.219397</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000922</v>
+        <v>0.000579</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1110,16 +1110,16 @@
         <v>0.002797</v>
       </c>
       <c r="G18" t="n">
-        <v>8.772275</v>
+        <v>12.42672</v>
       </c>
       <c r="H18" t="n">
-        <v>0.035925</v>
+        <v>5.242734</v>
       </c>
       <c r="I18" t="n">
-        <v>0.004728</v>
+        <v>0.014317</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000283</v>
+        <v>0.001782</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1148,16 +1148,16 @@
         <v>0.002095</v>
       </c>
       <c r="G19" t="n">
-        <v>4.674549</v>
+        <v>11.701162</v>
       </c>
       <c r="H19" t="n">
-        <v>0.023037</v>
+        <v>0.410918</v>
       </c>
       <c r="I19" t="n">
-        <v>0.056326</v>
+        <v>0.203749</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000312</v>
+        <v>0.036343</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1186,16 +1186,16 @@
         <v>0.003654</v>
       </c>
       <c r="G20" t="n">
-        <v>0.065326</v>
+        <v>0.230595</v>
       </c>
       <c r="H20" t="n">
-        <v>0.015522</v>
+        <v>0.0485</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000457</v>
+        <v>0.001245</v>
       </c>
       <c r="J20" t="n">
-        <v>6.9e-05</v>
+        <v>5.2e-05</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1224,16 +1224,16 @@
         <v>0.004063</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08334</v>
+        <v>0.282988</v>
       </c>
       <c r="H21" t="n">
-        <v>0.014733</v>
+        <v>0.100313</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000507</v>
+        <v>0.000556</v>
       </c>
       <c r="J21" t="n">
-        <v>8.4e-05</v>
+        <v>0.000215</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SVM_rbf</t>
+          <t>SVC_rbf</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1262,16 +1262,16 @@
         <v>0.003156</v>
       </c>
       <c r="G22" t="n">
-        <v>1.302678</v>
+        <v>5.050632</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0074</v>
+        <v>0.113066</v>
       </c>
       <c r="I22" t="n">
-        <v>1.251402</v>
+        <v>4.790706</v>
       </c>
       <c r="J22" t="n">
-        <v>0.003358</v>
+        <v>0.090618</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1300,16 +1300,16 @@
         <v>0.003686</v>
       </c>
       <c r="G23" t="n">
-        <v>0.565312</v>
+        <v>1.350152</v>
       </c>
       <c r="H23" t="n">
-        <v>0.004434</v>
+        <v>0.043733</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001191</v>
+        <v>0.002659</v>
       </c>
       <c r="J23" t="n">
-        <v>9.3e-05</v>
+        <v>0.000226</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1338,16 +1338,16 @@
         <v>0.00175</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004109</v>
+        <v>0.055863</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00155</v>
+        <v>0.000974</v>
       </c>
       <c r="I24" t="n">
-        <v>0.245896</v>
+        <v>1.365166</v>
       </c>
       <c r="J24" t="n">
-        <v>0.003989</v>
+        <v>0.017195</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1376,16 +1376,16 @@
         <v>0.001882</v>
       </c>
       <c r="G25" t="n">
-        <v>12.727097</v>
+        <v>12.875312</v>
       </c>
       <c r="H25" t="n">
-        <v>0.252151</v>
+        <v>0.3913</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004829</v>
+        <v>0.00504</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000255</v>
+        <v>0.000258</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1414,16 +1414,16 @@
         <v>0.002814</v>
       </c>
       <c r="G26" t="n">
-        <v>6.156286</v>
+        <v>6.031919</v>
       </c>
       <c r="H26" t="n">
-        <v>0.007215</v>
+        <v>0.007511</v>
       </c>
       <c r="I26" t="n">
-        <v>0.055212</v>
+        <v>0.056565</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001072</v>
+        <v>0.002444</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1452,16 +1452,16 @@
         <v>0.004347</v>
       </c>
       <c r="G27" t="n">
-        <v>0.083574</v>
+        <v>0.08805</v>
       </c>
       <c r="H27" t="n">
-        <v>0.006024</v>
+        <v>0.00553</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001029</v>
+        <v>0.00077</v>
       </c>
       <c r="J27" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1490,16 +1490,16 @@
         <v>0.003596</v>
       </c>
       <c r="G28" t="n">
-        <v>0.181578</v>
+        <v>0.159093</v>
       </c>
       <c r="H28" t="n">
-        <v>0.013659</v>
+        <v>0.020408</v>
       </c>
       <c r="I28" t="n">
-        <v>0.001067</v>
+        <v>0.000806</v>
       </c>
       <c r="J28" t="n">
-        <v>0.000279</v>
+        <v>6.4e-05</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SVM_rbf</t>
+          <t>SVC_rbf</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1528,16 +1528,16 @@
         <v>0.002873</v>
       </c>
       <c r="G29" t="n">
-        <v>1.470116</v>
+        <v>1.487484</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05199</v>
+        <v>0.053612</v>
       </c>
       <c r="I29" t="n">
-        <v>1.586316</v>
+        <v>1.584973</v>
       </c>
       <c r="J29" t="n">
-        <v>0.001784</v>
+        <v>0.009112</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>

--- a/results/model_results.xlsx
+++ b/results/model_results.xlsx
@@ -502,16 +502,16 @@
         <v>0.003278</v>
       </c>
       <c r="G2" t="n">
-        <v>0.364895</v>
+        <v>0.372869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004326</v>
+        <v>0.006357</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000791</v>
+        <v>0.000789</v>
       </c>
       <c r="J2" t="n">
-        <v>7.6e-05</v>
+        <v>6.7e-05</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -540,16 +540,16 @@
         <v>0.002741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.048774</v>
+        <v>0.047192</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004747</v>
+        <v>0.001022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.178129</v>
+        <v>0.193657</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00014</v>
+        <v>0.001389</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -578,16 +578,16 @@
         <v>0.00232</v>
       </c>
       <c r="G4" t="n">
-        <v>9.730859000000001</v>
+        <v>9.764949</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0593</v>
+        <v>0.22316</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004879</v>
+        <v>0.005531</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000155</v>
+        <v>0.001332</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -616,16 +616,16 @@
         <v>0.001667</v>
       </c>
       <c r="G5" t="n">
-        <v>5.622407</v>
+        <v>5.586229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.039901</v>
+        <v>0.014908</v>
       </c>
       <c r="I5" t="n">
-        <v>0.051366</v>
+        <v>0.052141</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000351</v>
+        <v>0.000286</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -654,16 +654,16 @@
         <v>0.003442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.053402</v>
+        <v>0.05267</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005595</v>
+        <v>0.003853</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000456</v>
+        <v>0.000506</v>
       </c>
       <c r="J6" t="n">
-        <v>9.1e-05</v>
+        <v>0.000102</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -692,16 +692,16 @@
         <v>0.003035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.080661</v>
+        <v>0.066134</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006309</v>
+        <v>0.004496</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000489</v>
+        <v>0.000455</v>
       </c>
       <c r="J7" t="n">
-        <v>8.2e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -730,16 +730,16 @@
         <v>0.003481</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275501</v>
+        <v>1.281229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.029185</v>
+        <v>0.028756</v>
       </c>
       <c r="I8" t="n">
-        <v>1.193824</v>
+        <v>1.183465</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001193</v>
+        <v>0.001818</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -768,16 +768,16 @@
         <v>0.002512</v>
       </c>
       <c r="G9" t="n">
-        <v>1.021407</v>
+        <v>1.019927</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006684</v>
+        <v>0.005123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001169</v>
+        <v>0.001268</v>
       </c>
       <c r="J9" t="n">
-        <v>6.3e-05</v>
+        <v>0.000136</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -806,16 +806,16 @@
         <v>0.001514</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004943</v>
+        <v>0.005852</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001205</v>
+        <v>0.002059</v>
       </c>
       <c r="I10" t="n">
-        <v>1.160957</v>
+        <v>1.462584</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2791</v>
+        <v>1.714401</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -844,16 +844,16 @@
         <v>0.001624</v>
       </c>
       <c r="G11" t="n">
-        <v>10.80929</v>
+        <v>10.570345</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09884900000000001</v>
+        <v>0.061104</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004715</v>
+        <v>0.005308</v>
       </c>
       <c r="J11" t="n">
-        <v>6.4e-05</v>
+        <v>0.000176</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -882,16 +882,16 @@
         <v>0.002053</v>
       </c>
       <c r="G12" t="n">
-        <v>9.53619</v>
+        <v>9.564855</v>
       </c>
       <c r="H12" t="n">
-        <v>0.017483</v>
+        <v>0.022064</v>
       </c>
       <c r="I12" t="n">
-        <v>0.049963</v>
+        <v>0.051117</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000141</v>
+        <v>0.000162</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -920,16 +920,16 @@
         <v>0.002754</v>
       </c>
       <c r="G13" t="n">
-        <v>0.093955</v>
+        <v>0.0983</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001262</v>
+        <v>0.006989</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0009970000000000001</v>
+        <v>0.000915</v>
       </c>
       <c r="J13" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>0.000102</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -958,16 +958,16 @@
         <v>0.002782</v>
       </c>
       <c r="G14" t="n">
-        <v>0.159695</v>
+        <v>0.182668</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005341</v>
+        <v>0.01066</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000926</v>
+        <v>0.001002</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000116</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -996,16 +996,16 @@
         <v>0.00302</v>
       </c>
       <c r="G15" t="n">
-        <v>1.192658</v>
+        <v>1.147476</v>
       </c>
       <c r="H15" t="n">
-        <v>0.033586</v>
+        <v>0.003484</v>
       </c>
       <c r="I15" t="n">
-        <v>1.146287</v>
+        <v>1.143951</v>
       </c>
       <c r="J15" t="n">
-        <v>0.004474</v>
+        <v>0.006981</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1034,16 +1034,16 @@
         <v>0.003106</v>
       </c>
       <c r="G16" t="n">
-        <v>0.274216</v>
+        <v>0.272693</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004364</v>
+        <v>0.001424</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000822</v>
+        <v>0.000781</v>
       </c>
       <c r="J16" t="n">
-        <v>9.8e-05</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
         <v>0.00226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04798</v>
+        <v>0.048245</v>
       </c>
       <c r="H17" t="n">
-        <v>0.004462</v>
+        <v>0.004199</v>
       </c>
       <c r="I17" t="n">
-        <v>0.219397</v>
+        <v>0.218724</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000579</v>
+        <v>0.000891</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1110,16 +1110,16 @@
         <v>0.002797</v>
       </c>
       <c r="G18" t="n">
-        <v>12.42672</v>
+        <v>8.734971</v>
       </c>
       <c r="H18" t="n">
-        <v>5.242734</v>
+        <v>0.037517</v>
       </c>
       <c r="I18" t="n">
-        <v>0.014317</v>
+        <v>0.004576</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001782</v>
+        <v>0.000148</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1148,16 +1148,16 @@
         <v>0.002095</v>
       </c>
       <c r="G19" t="n">
-        <v>11.701162</v>
+        <v>4.618773</v>
       </c>
       <c r="H19" t="n">
-        <v>0.410918</v>
+        <v>0.022338</v>
       </c>
       <c r="I19" t="n">
-        <v>0.203749</v>
+        <v>0.055327</v>
       </c>
       <c r="J19" t="n">
-        <v>0.036343</v>
+        <v>0.000466</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1186,16 +1186,16 @@
         <v>0.003654</v>
       </c>
       <c r="G20" t="n">
-        <v>0.230595</v>
+        <v>0.057161</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0485</v>
+        <v>0.004205</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001245</v>
+        <v>0.000458</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1224,16 +1224,16 @@
         <v>0.004063</v>
       </c>
       <c r="G21" t="n">
-        <v>0.282988</v>
+        <v>0.085401</v>
       </c>
       <c r="H21" t="n">
-        <v>0.100313</v>
+        <v>0.000639</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000556</v>
+        <v>0.000462</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000215</v>
+        <v>8.6e-05</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1262,16 +1262,16 @@
         <v>0.003156</v>
       </c>
       <c r="G22" t="n">
-        <v>5.050632</v>
+        <v>1.314718</v>
       </c>
       <c r="H22" t="n">
-        <v>0.113066</v>
+        <v>0.044777</v>
       </c>
       <c r="I22" t="n">
-        <v>4.790706</v>
+        <v>1.272803</v>
       </c>
       <c r="J22" t="n">
-        <v>0.090618</v>
+        <v>0.015998</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1300,16 +1300,16 @@
         <v>0.003686</v>
       </c>
       <c r="G23" t="n">
-        <v>1.350152</v>
+        <v>0.566483</v>
       </c>
       <c r="H23" t="n">
-        <v>0.043733</v>
+        <v>0.001321</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002659</v>
+        <v>0.001169</v>
       </c>
       <c r="J23" t="n">
-        <v>0.000226</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1338,16 +1338,16 @@
         <v>0.00175</v>
       </c>
       <c r="G24" t="n">
-        <v>0.055863</v>
+        <v>0.005624</v>
       </c>
       <c r="H24" t="n">
-        <v>0.000974</v>
+        <v>0.001495</v>
       </c>
       <c r="I24" t="n">
-        <v>1.365166</v>
+        <v>0.258431</v>
       </c>
       <c r="J24" t="n">
-        <v>0.017195</v>
+        <v>0.015056</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1376,16 +1376,16 @@
         <v>0.001882</v>
       </c>
       <c r="G25" t="n">
-        <v>12.875312</v>
+        <v>12.345798</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3913</v>
+        <v>0.015576</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00504</v>
+        <v>0.005143</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000258</v>
+        <v>6e-05</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1414,16 +1414,16 @@
         <v>0.002814</v>
       </c>
       <c r="G26" t="n">
-        <v>6.031919</v>
+        <v>5.995529</v>
       </c>
       <c r="H26" t="n">
-        <v>0.007511</v>
+        <v>0.007133</v>
       </c>
       <c r="I26" t="n">
-        <v>0.056565</v>
+        <v>0.05431</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002444</v>
+        <v>0.000771</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1452,16 +1452,16 @@
         <v>0.004347</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08805</v>
+        <v>0.078739</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00553</v>
+        <v>0.000438</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00077</v>
+        <v>0.000942</v>
       </c>
       <c r="J27" t="n">
-        <v>9.8e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1490,16 +1490,16 @@
         <v>0.003596</v>
       </c>
       <c r="G28" t="n">
-        <v>0.159093</v>
+        <v>0.146206</v>
       </c>
       <c r="H28" t="n">
-        <v>0.020408</v>
+        <v>0.004251</v>
       </c>
       <c r="I28" t="n">
-        <v>0.000806</v>
+        <v>0.000762</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4e-05</v>
+        <v>0.000126</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1528,16 +1528,16 @@
         <v>0.002873</v>
       </c>
       <c r="G29" t="n">
-        <v>1.487484</v>
+        <v>1.438382</v>
       </c>
       <c r="H29" t="n">
-        <v>0.053612</v>
+        <v>0.017184</v>
       </c>
       <c r="I29" t="n">
-        <v>1.584973</v>
+        <v>1.574721</v>
       </c>
       <c r="J29" t="n">
-        <v>0.009112</v>
+        <v>0.000142</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
